--- a/safety_inspection_forms/027_site_safety_officer_check_in_form--safety_inspection_forms.xlsx
+++ b/safety_inspection_forms/027_site_safety_officer_check_in_form--safety_inspection_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="30" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -620,11 +620,7 @@
           <t>Check In Date</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>YYYY-MM-DD</t>
-        </is>
-      </c>
+      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>no</t>
@@ -647,11 +643,7 @@
           <t>Check In Time</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>HH:MM AM/PM</t>
-        </is>
-      </c>
+      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>no</t>
@@ -763,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Weather Conditions</t>
+          <t>Incident Reports</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -776,7 +768,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -786,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Incident Reports</t>
+          <t>Safety Officer Availability</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -809,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Incident Reports</t>
+          <t>Site Safety Officer Check In Form Page 13</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -822,7 +814,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>select_one</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -832,264 +824,11 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Safety Officer</t>
+          <t>Site Conditions</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_15</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Safety Officer</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_16</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Weather Conditions</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_17</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Weather Conditions</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_18</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Safety Officer</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_19</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Safety Officer</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_20</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Site Conditions</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_21</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Site Conditions</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_22</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Weather Conditions</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_23</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Weather Conditions</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_24</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Safety Officer</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>select_one</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_25</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Safety Officer</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1106,11 +845,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C35"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="2" max="2"/>
     <col width="7" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -1139,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1156,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1173,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1190,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1207,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1224,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1241,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1258,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1326,386 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_15_choices</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_16_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_17_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_18_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_19_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_20_choices</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_21_choices</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_22_choices</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_23_choices</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_24_choices</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>site_safety_officer_check_in_form_page_25_choices</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>No</t>
+          <t>False</t>
         </is>
       </c>
     </row>
